--- a/00soportes/empresas_gijon.xlsx
+++ b/00soportes/empresas_gijon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\bazop\projects\cvpetrix2022\00soportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B2B23D-1083-419D-8086-89A332FB11D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34093052-D7FD-400B-83CF-6EE9A6059F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-10780" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Hoja3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$K$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="202">
   <si>
     <t>empresa</t>
   </si>
@@ -623,6 +623,33 @@
   </si>
   <si>
     <t>C. Marqués de San Esteban, 25 Bajo. Gijón. Asturias</t>
+  </si>
+  <si>
+    <t>Nunsys</t>
+  </si>
+  <si>
+    <t>C. Leopoldo Alas, 55 33204</t>
+  </si>
+  <si>
+    <t>https://gystic.es</t>
+  </si>
+  <si>
+    <t>https://www.neamaster.com/sobre-nosotros/</t>
+  </si>
+  <si>
+    <t>Nea Master</t>
+  </si>
+  <si>
+    <t>contacto@neamaster.com</t>
+  </si>
+  <si>
+    <t>Ovideo | Gijón</t>
+  </si>
+  <si>
+    <t>OVIEDO: c/ La Corredoria, 55, Edif. Trébol – 33211 | GIJÓN: c/ Álava, 80– 33011</t>
+  </si>
+  <si>
+    <t>Fecha</t>
   </si>
 </sst>
 </file>
@@ -693,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -703,6 +730,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -995,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -1006,10 +1035,11 @@
     <col min="6" max="6" width="17.44140625" customWidth="1"/>
     <col min="7" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.21875" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -1035,13 +1065,16 @@
         <v>26</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1064,7 +1097,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1084,7 +1117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1107,7 +1140,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1130,7 +1163,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1153,7 +1186,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1170,7 +1203,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1196,7 +1229,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1219,7 +1252,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1236,7 +1269,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -1256,7 +1289,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -1275,11 +1308,11 @@
       <c r="G12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1305,7 +1338,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1325,7 +1358,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1345,7 +1378,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1365,7 +1398,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1385,7 +1418,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1405,7 +1438,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1425,7 +1458,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1444,11 +1477,11 @@
       <c r="G20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I20" t="s">
+      <c r="J20" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1465,7 +1498,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -1491,7 +1524,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -1514,7 +1547,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -1539,11 +1572,11 @@
       <c r="H24" t="s">
         <v>156</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1568,11 +1601,11 @@
       <c r="H25" t="s">
         <v>156</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1591,11 +1624,11 @@
       <c r="G26" t="s">
         <v>108</v>
       </c>
-      <c r="I26" t="s">
+      <c r="J26" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>26</v>
       </c>
@@ -1620,11 +1653,11 @@
       <c r="H27" t="s">
         <v>152</v>
       </c>
-      <c r="I27" t="s">
+      <c r="J27" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>27</v>
       </c>
@@ -1649,11 +1682,11 @@
       <c r="H28" t="s">
         <v>156</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1672,14 +1705,14 @@
       <c r="G29" t="s">
         <v>131</v>
       </c>
-      <c r="I29" t="s">
+      <c r="J29" t="s">
         <v>132</v>
       </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1698,14 +1731,14 @@
       <c r="G30" t="s">
         <v>136</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" t="s">
         <v>137</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1727,14 +1760,14 @@
       <c r="G31" t="s">
         <v>142</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
         <v>144</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1753,14 +1786,14 @@
       <c r="G32" t="s">
         <v>149</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>150</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -1783,7 +1816,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1797,7 +1830,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1817,7 +1850,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1837,7 +1870,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1854,7 +1887,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1871,7 +1904,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -1888,7 +1921,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -1908,7 +1941,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -1925,16 +1958,63 @@
         <v>71</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>21</v>
+      <c r="B42" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D42" t="s">
+        <v>194</v>
+      </c>
+      <c r="E42" t="s">
+        <v>70</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H42" t="s">
+        <v>156</v>
+      </c>
+      <c r="I42" s="7">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D43" t="s">
+        <v>200</v>
+      </c>
+      <c r="E43" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H43" t="s">
+        <v>156</v>
+      </c>
+      <c r="I43" s="8">
+        <v>46310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J32" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K32" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -1971,6 +2051,9 @@
     <hyperlink ref="G35" r:id="rId25" xr:uid="{7B20D71D-A8E4-4770-A904-E7F0195131B8}"/>
     <hyperlink ref="G36" r:id="rId26" xr:uid="{D5EC4F47-86E4-4718-9F94-4828CCA7BCAA}"/>
     <hyperlink ref="G40" r:id="rId27" xr:uid="{B7FA97EE-2A65-4884-B3BB-BE558C27799E}"/>
+    <hyperlink ref="G42" r:id="rId28" xr:uid="{697622C4-5C42-4902-869D-A6026A1AC7B7}"/>
+    <hyperlink ref="G43" r:id="rId29" xr:uid="{FF79F91A-E299-447D-971B-10C674ACD147}"/>
+    <hyperlink ref="F43" r:id="rId30" xr:uid="{A95E679B-4D49-4071-8E82-72A722245BEE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/00soportes/empresas_gijon.xlsx
+++ b/00soportes/empresas_gijon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\bazop\projects\cvpetrix2022\00soportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34093052-D7FD-400B-83CF-6EE9A6059F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8DED95-F8F6-4872-8A46-D740F7A706A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-10780" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="218">
   <si>
     <t>empresa</t>
   </si>
@@ -650,6 +650,54 @@
   </si>
   <si>
     <t>Fecha</t>
+  </si>
+  <si>
+    <t>https://clustertic.net</t>
+  </si>
+  <si>
+    <t>Gijón Science and Technology Park | 33394 Gijón</t>
+  </si>
+  <si>
+    <t>info@clustertic.net</t>
+  </si>
+  <si>
+    <t>Cluster TIC Asturias</t>
+  </si>
+  <si>
+    <t>https://bisoul.es</t>
+  </si>
+  <si>
+    <t>Bisoul</t>
+  </si>
+  <si>
+    <t>Calle Periodista Paco Ignacio Taibo Lavilla, 1 (Zona Viesques / El Coto), 33204 Gijón, Asturias.</t>
+  </si>
+  <si>
+    <t>hola@bisoul.es</t>
+  </si>
+  <si>
+    <t>KPR Soluciones Web</t>
+  </si>
+  <si>
+    <t>https://www.kprweb.com</t>
+  </si>
+  <si>
+    <t>Calle Marqués de San Esteban, 18, 3º Izquierda | 33206 Gijón, Asturias</t>
+  </si>
+  <si>
+    <t>Gapivedia</t>
+  </si>
+  <si>
+    <t>Parque Científico Tecnológico de Gijón (Edificio Vorágine, C/ Profesor Potter 183, 33203 Gijón, Asturias)</t>
+  </si>
+  <si>
+    <t>Civilnova Solutions</t>
+  </si>
+  <si>
+    <t>https://www.civilnova.com</t>
+  </si>
+  <si>
+    <t>Calle Profesor Potter, 72, 1ª Planta, Oficina 1.6  | Parque Científico Tecnológico de Gijón (PCTI) | 33394 Gijón, Asturias</t>
   </si>
 </sst>
 </file>
@@ -720,7 +768,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -732,6 +780,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1024,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -2013,9 +2062,145 @@
         <v>46310</v>
       </c>
     </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D44" t="s">
+        <v>203</v>
+      </c>
+      <c r="E44" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H44" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" s="7">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" t="s">
+        <v>70</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H45" t="s">
+        <v>156</v>
+      </c>
+      <c r="I45" s="7">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" t="s">
+        <v>212</v>
+      </c>
+      <c r="E46" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H46" t="s">
+        <v>156</v>
+      </c>
+      <c r="I46" s="7">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D47" t="s">
+        <v>214</v>
+      </c>
+      <c r="E47" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H47" t="s">
+        <v>152</v>
+      </c>
+      <c r="I47" s="7">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D48" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H48" t="s">
+        <v>156</v>
+      </c>
+      <c r="I48" s="7">
+        <v>46318</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K32" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C1:C1048576 F45">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -2054,6 +2239,13 @@
     <hyperlink ref="G42" r:id="rId28" xr:uid="{697622C4-5C42-4902-869D-A6026A1AC7B7}"/>
     <hyperlink ref="G43" r:id="rId29" xr:uid="{FF79F91A-E299-447D-971B-10C674ACD147}"/>
     <hyperlink ref="F43" r:id="rId30" xr:uid="{A95E679B-4D49-4071-8E82-72A722245BEE}"/>
+    <hyperlink ref="G44" r:id="rId31" xr:uid="{48AE2E04-2D6F-4B5E-A74B-4D1ED306F4FF}"/>
+    <hyperlink ref="F44" r:id="rId32" xr:uid="{73B04AA7-DE4A-479E-A04C-AF57272CF457}"/>
+    <hyperlink ref="G45" r:id="rId33" xr:uid="{0DE97A0E-DEBB-465A-A9E1-44099AC0A982}"/>
+    <hyperlink ref="F45" r:id="rId34" xr:uid="{0D079489-177B-49D0-A798-6F68E19118DE}"/>
+    <hyperlink ref="G46" r:id="rId35" xr:uid="{32EE1C80-3170-4C18-A91E-19817193837C}"/>
+    <hyperlink ref="G47" r:id="rId36" xr:uid="{650601A4-131C-4734-840A-93AFC6ADDB7B}"/>
+    <hyperlink ref="G48" r:id="rId37" xr:uid="{266CE803-6EF6-4B96-8328-96FB6C0F236C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
